--- a/Config/Excel/GameConfig/EmitterConfig.xlsx
+++ b/Config/Excel/GameConfig/EmitterConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26260" windowHeight="12720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="12720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EmitterConfig" sheetId="1" state="visible" r:id="rId1"/>
@@ -1031,14 +1031,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22.9134615384615" customWidth="1" min="3" max="3"/>
     <col width="24.6730769230769" customWidth="1" min="4" max="4"/>
     <col width="51.9230769230769" customWidth="1" min="8" max="8"/>
     <col width="24.5192307692308" customWidth="1" min="13" max="13"/>
-    <col width="52.7211538461538" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
+    <col width="19.5480769230769" customWidth="1" min="15" max="15"/>
+    <col width="25.6442307692308" customWidth="1" min="16" max="16"/>
+    <col width="17.9423076923077" customWidth="1" min="17" max="17"/>
+    <col width="18.9038461538462" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1084,82 +1088,62 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>CooldownMs</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>CanMoveCast</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>CanMoveCast</t>
+          <t>NeedExplicitTarget</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>NeedExplicitTarget</t>
+          <t>IsEnabled</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>IsEnabled</t>
+          <t>ProjectileSpeed</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ProjectileSpeed</t>
+          <t>ProjectileMaxDistance</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>ProjectileMaxDistance</t>
+          <t>ProjectileCollisionRadius</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ProjectileCollisionRadius</t>
+          <t>ProjectilePiercing</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ProjectilePiercing</t>
+          <t>ProjectileMaxHitCount</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ProjectileMaxHitCount</t>
+          <t>Desc</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t>UpgradeConfigId</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>AttackHitRatio</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>UpgradeConfigId</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
           <t>BuffSlotCount</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>BaseDamage</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>WhiteAttackRatio</t>
         </is>
       </c>
     </row>
@@ -1211,77 +1195,57 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>float</t>
         </is>
       </c>
     </row>
@@ -1328,82 +1292,62 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>冷却毫秒</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>是否可移动施法</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>是否可移动施法</t>
+          <t>是否必须显式指定目标</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>是否必须显式指定目标</t>
+          <t>是否启用</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>是否启用</t>
+          <t>投射物飞行速度（单位/秒）</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>投射物飞行速度（单位/秒）</t>
+          <t>投射物最大飞行距离</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>投射物最大飞行距离</t>
+          <t>投射物碰撞半径</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>投射物碰撞半径</t>
+          <t>投射物是否穿透</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>投射物是否穿透</t>
+          <t>投射物最大命中单位数</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>投射物最大命中单位数</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>升级方案ID</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>攻击动画命中点比例</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>升级方案ID</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>Buff槽位数量</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>白值基础伤害</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>白值攻击力系数</t>
         </is>
       </c>
     </row>
@@ -1432,54 +1376,42 @@
         <v>11001</v>
       </c>
       <c r="I4" t="n">
-        <v>550</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
-      </c>
-      <c r="P4" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>玩家白值发射器：低冷却、稳定清怪节奏</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>11001</v>
+      </c>
       <c r="T4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>12001</v>
-      </c>
-      <c r="V4" t="n">
         <v>3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1507,54 +1439,42 @@
         <v>21001</v>
       </c>
       <c r="I5" t="n">
-        <v>1650</v>
-      </c>
-      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
-      </c>
-      <c r="P5" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>普通怪物白值攻击底盘</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>21001</v>
+      </c>
       <c r="T5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1582,54 +1502,42 @@
         <v>21002</v>
       </c>
       <c r="I6" t="n">
-        <v>1450</v>
-      </c>
-      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P6" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>精英怪物白值攻击底盘</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>21002</v>
+      </c>
       <c r="T6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1657,54 +1565,42 @@
         <v>21003</v>
       </c>
       <c r="I7" t="n">
-        <v>1900</v>
-      </c>
-      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Boss白值攻击底盘</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>21003</v>
+      </c>
       <c r="T7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>8</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1732,54 +1628,42 @@
         <v>11002</v>
       </c>
       <c r="I8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J8" t="n">
         <v>2</v>
       </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
-      </c>
-      <c r="P8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>玩家白值发射器：中等冷却，适合作为稳定输出底盘</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>11002</v>
+      </c>
       <c r="T8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12001</v>
-      </c>
-      <c r="V8" t="n">
         <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1807,54 +1691,42 @@
         <v>11003</v>
       </c>
       <c r="I9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J9" t="n">
         <v>3</v>
       </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
-      </c>
-      <c r="P9" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>玩家白值发射器：较长冷却，突出单次命中节奏</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>11003</v>
+      </c>
       <c r="T9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>12001</v>
-      </c>
-      <c r="V9" t="n">
         <v>3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1882,54 +1754,42 @@
         <v>11004</v>
       </c>
       <c r="I10" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J10" t="n">
         <v>4</v>
       </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
-      </c>
-      <c r="P10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>玩家白值发射器：间隔释放，适合观察高间隔输出手感</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>11004</v>
+      </c>
       <c r="T10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>12001</v>
-      </c>
-      <c r="V10" t="n">
         <v>3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1957,19 +1817,19 @@
         <v>11005</v>
       </c>
       <c r="I11" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J11" t="n">
         <v>5</v>
       </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1977,34 +1837,22 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>玩家白值发射器：自用测试底盘，不携带治疗效果</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>11005</v>
+      </c>
       <c r="T11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>12001</v>
-      </c>
-      <c r="V11" t="n">
         <v>3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2032,54 +1880,42 @@
         <v>21004</v>
       </c>
       <c r="I12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
-      </c>
-      <c r="P12" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>怪物白值攻击底盘：用于压制节奏测试</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>21004</v>
+      </c>
       <c r="T12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2107,54 +1943,42 @@
         <v>21005</v>
       </c>
       <c r="I13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J13" t="n">
         <v>2</v>
       </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
-      </c>
-      <c r="P13" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>怪物白值攻击底盘：名称保留行为定位，不内置控制效果</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>21005</v>
+      </c>
       <c r="T13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2182,54 +2006,42 @@
         <v>21006</v>
       </c>
       <c r="I14" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
-      </c>
-      <c r="P14" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>Boss白值攻击底盘：高压节奏测试</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>21006</v>
+      </c>
       <c r="T14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2257,54 +2069,42 @@
         <v>21007</v>
       </c>
       <c r="I15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J15" t="n">
         <v>2</v>
       </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
-      </c>
-      <c r="P15" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>Boss白值攻击底盘：爆发节奏测试</t>
         </is>
       </c>
+      <c r="S15" t="n">
+        <v>21007</v>
+      </c>
       <c r="T15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>12000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
